--- a/Data General Nova 1200 Restoration/DG_4046_4047_Cables/Bill_of_Materials_4047-to-4046_Connectors.xlsx
+++ b/Data General Nova 1200 Restoration/DG_4046_4047_Cables/Bill_of_Materials_4047-to-4046_Connectors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/288ee42248ca7e9c/Documents/Vintage Computer other/Data General/Add-on Boards Nova/4047 Logic Interface/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="8_{291863AF-43BD-4773-AC18-7AD65028538B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46AB9587-B505-45DC-B4A7-3C0BDD5C7871}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="8_{291863AF-43BD-4773-AC18-7AD65028538B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B57E7B61-9164-401D-A753-BA11CE09F33C}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="3130" windowWidth="29050" windowHeight="10760" tabRatio="621" xr2:uid="{00C607E4-F5CA-4B88-8F75-FEAFAF39518F}"/>
+    <workbookView xWindow="2400" yWindow="6070" windowWidth="26780" windowHeight="15560" tabRatio="621" xr2:uid="{00C607E4-F5CA-4B88-8F75-FEAFAF39518F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>Qty</t>
   </si>
@@ -195,6 +195,18 @@
   </si>
   <si>
     <t>Ref. Des.</t>
+  </si>
+  <si>
+    <t>Harting</t>
+  </si>
+  <si>
+    <t>09185266927</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/harting/09185266927/4336265</t>
+  </si>
+  <si>
+    <t>Header, 26-pin, vertical, with wire-wrap pins</t>
   </si>
 </sst>
 </file>
@@ -271,7 +283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -314,6 +326,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -641,7 +655,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.54296875" style="1" customWidth="1"/>
@@ -931,8 +945,8 @@
       <c r="O11" s="15"/>
       <c r="P11" s="14"/>
       <c r="Q11" s="16">
-        <f>SUM(P11:P14)</f>
-        <v>14.089942105263155</v>
+        <f>SUM(P11:P15)</f>
+        <v>0.90004210526315787</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.35">
@@ -969,13 +983,13 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="F13" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="J13" t="s">
         <v>39</v>
@@ -995,133 +1009,162 @@
       </c>
       <c r="P13" s="4">
         <f>F13*O13</f>
-        <v>13.189899999999998</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="7"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B15" s="11" t="s">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="4">
+        <f>11.01*1.0775+(6.99/2/4)</f>
+        <v>12.737024999999997</v>
+      </c>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="22"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="16">
-        <f>SUM(P15:P17)</f>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="16">
+        <f>SUM(P16:P18)</f>
         <v>15.6</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="F16" s="2">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H17" t="s">
         <v>44</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J17" t="s">
         <v>12</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K17" t="s">
         <v>12</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L17" t="s">
         <v>45</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="4">
+      <c r="O17" s="4">
         <v>7.8</v>
       </c>
-      <c r="P16" s="4">
-        <f t="shared" ref="P16" si="2">F16*O16</f>
+      <c r="P17" s="4">
+        <f t="shared" ref="P17" si="2">F17*O17</f>
         <v>15.6</v>
       </c>
-      <c r="Q16" s="7"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B18" s="11" t="s">
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="16">
-        <f>SUM(P18:P20)</f>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="16">
+        <f>SUM(P19:P21)</f>
         <v>27.75</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="F19" s="2">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="F20" s="2">
         <v>1</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H20" t="s">
         <v>33</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J20" t="s">
         <v>42</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K20" t="s">
         <v>43</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L20" t="s">
         <v>6</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="O19" s="4">
+      <c r="O20" s="4">
         <v>27.75</v>
       </c>
-      <c r="P19" s="4">
-        <f t="shared" ref="P19" si="3">F19*O19</f>
+      <c r="P20" s="4">
+        <f t="shared" ref="P20" si="3">F20*O20</f>
         <v>27.75</v>
       </c>
-      <c r="Q19" s="7"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B21" s="17" t="s">
+      <c r="Q20" s="7"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B22" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="21">
-        <f>SUM(Q3:Q20)</f>
-        <v>94.828374999999994</v>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="21">
+        <f>SUM(Q3:Q21)</f>
+        <v>81.638475</v>
       </c>
     </row>
   </sheetData>
@@ -1131,10 +1174,11 @@
     <hyperlink ref="M5" r:id="rId3" xr:uid="{3AED3022-B9A9-43BE-93EC-7EF449C6A895}"/>
     <hyperlink ref="M9" r:id="rId4" xr:uid="{774E71D1-B2FF-4693-8BBC-23C6FC596D79}"/>
     <hyperlink ref="M13" r:id="rId5" xr:uid="{0A8C1BB0-EE7A-423D-A7A3-9DA56F9C5B95}"/>
-    <hyperlink ref="M19" r:id="rId6" xr:uid="{4943A98A-4350-4A7C-B056-1F7F9D5468F1}"/>
-    <hyperlink ref="M16" r:id="rId7" xr:uid="{2E3B58F8-C580-4DF0-B6A0-1BFEB6175F83}"/>
+    <hyperlink ref="M20" r:id="rId6" xr:uid="{4943A98A-4350-4A7C-B056-1F7F9D5468F1}"/>
+    <hyperlink ref="M17" r:id="rId7" xr:uid="{2E3B58F8-C580-4DF0-B6A0-1BFEB6175F83}"/>
+    <hyperlink ref="M14" r:id="rId8" xr:uid="{E8E62168-5D60-47F2-910E-1D22371BFA97}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
 </worksheet>
 </file>